--- a/Outputs/Scenarios/PtX_demand_LU_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LU_Electrification.xlsx
@@ -803,7 +803,7 @@
         <v>0.0009583835277984213</v>
       </c>
       <c r="G10" t="n">
-        <v>5.625438470382552e-06</v>
+        <v>5.625438470382551e-06</v>
       </c>
       <c r="H10" t="n">
         <v>0.0006338538975374</v>
@@ -840,7 +840,7 @@
         <v>0.00945183538245817</v>
       </c>
       <c r="G11" t="n">
-        <v>3.961831351454017e-05</v>
+        <v>3.961831351454016e-05</v>
       </c>
       <c r="H11" t="n">
         <v>0.005793082853467901</v>
@@ -1555,7 +1555,7 @@
         <v>4.848221138366855e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>4.135597056324283e-05</v>
+        <v>4.135597056324282e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001609770627996779</v>
+        <v>0.00160977062799678</v>
       </c>
       <c r="D31" t="n">
         <v>3.993022131207738e-05</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>6.892661760540472e-06</v>
+        <v>6.892661760540471e-06</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.757064704216189e-05</v>
+        <v>2.757064704216188e-05</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4.135597056324283e-05</v>
+        <v>4.135597056324282e-05</v>
       </c>
     </row>
     <row r="34">
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0008048853139983895</v>
+        <v>0.0008048853139983898</v>
       </c>
       <c r="D42" t="n">
         <v>3.194417704966191e-05</v>
@@ -1999,7 +1999,7 @@
         <v>2.551695335982555e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>6.892661760540472e-06</v>
+        <v>6.892661760540471e-06</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_LU_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LU_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>3.274988082656695e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>7.572262739075358e-06</v>
+        <v>1.734629245864163e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.262043789845893e-06</v>
+        <v>7.434125339417842e-07</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5.048175159383573e-06</v>
+        <v>2.973650135767137e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7.572262739075358e-06</v>
+        <v>2.973650135767137e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>2.624581556992121e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>1.388114958507361e-05</v>
+        <v>1.362792198666446e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>1.588659768611818e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>9.924060759973373e-05</v>
+        <v>9.743020561730947e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>4.718703464600818e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>1.262043789845893e-06</v>
+        <v>7.434125339417842e-07</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>4.848221138366855e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>4.135597056324282e-05</v>
+        <v>8.684753818280994e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>6.892661760540471e-06</v>
+        <v>3.722037350691856e-06</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.757064704216188e-05</v>
+        <v>1.488814940276742e-05</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4.135597056324282e-05</v>
+        <v>1.488814940276742e-05</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>2.551695335982555e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>6.892661760540471e-06</v>
+        <v>3.722037350691856e-06</v>
       </c>
     </row>
     <row r="43">
